--- a/db.xlsx
+++ b/db.xlsx
@@ -626,7 +626,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>2101</v>
+        <v>20101</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -649,7 +649,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>2102</v>
+        <v>20102</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -672,7 +672,7 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>2103</v>
+        <v>20103</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -695,7 +695,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>2104</v>
+        <v>20104</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -718,7 +718,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>2105</v>
+        <v>20105</v>
       </c>
       <c r="E6" t="s">
         <v>12</v>
@@ -741,7 +741,7 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>2106</v>
+        <v>20106</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -764,7 +764,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>2107</v>
+        <v>20107</v>
       </c>
       <c r="E8" t="s">
         <v>14</v>
@@ -787,7 +787,7 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>2108</v>
+        <v>20108</v>
       </c>
       <c r="E9" t="s">
         <v>15</v>
@@ -810,7 +810,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>2109</v>
+        <v>20109</v>
       </c>
       <c r="E10" t="s">
         <v>16</v>
@@ -833,7 +833,7 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>2110</v>
+        <v>20110</v>
       </c>
       <c r="E11" t="s">
         <v>17</v>
@@ -856,7 +856,7 @@
         <v>7</v>
       </c>
       <c r="D12">
-        <v>2111</v>
+        <v>20111</v>
       </c>
       <c r="E12" t="s">
         <v>18</v>
@@ -879,7 +879,7 @@
         <v>7</v>
       </c>
       <c r="D13">
-        <v>2112</v>
+        <v>20112</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
@@ -902,7 +902,7 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>2113</v>
+        <v>20113</v>
       </c>
       <c r="E14" t="s">
         <v>20</v>
@@ -925,7 +925,7 @@
         <v>7</v>
       </c>
       <c r="D15">
-        <v>2114</v>
+        <v>20114</v>
       </c>
       <c r="E15" t="s">
         <v>21</v>
@@ -948,7 +948,7 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>2115</v>
+        <v>20115</v>
       </c>
       <c r="E16" t="s">
         <v>22</v>
@@ -971,7 +971,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>2116</v>
+        <v>20116</v>
       </c>
       <c r="E17" t="s">
         <v>23</v>
@@ -994,7 +994,7 @@
         <v>7</v>
       </c>
       <c r="D18">
-        <v>2117</v>
+        <v>20117</v>
       </c>
       <c r="E18" t="s">
         <v>24</v>
@@ -1017,7 +1017,7 @@
         <v>7</v>
       </c>
       <c r="D19">
-        <v>2118</v>
+        <v>20118</v>
       </c>
       <c r="E19" t="s">
         <v>25</v>
@@ -1040,7 +1040,7 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>2119</v>
+        <v>20119</v>
       </c>
       <c r="E20" t="s">
         <v>26</v>
@@ -1063,7 +1063,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>2120</v>
+        <v>20120</v>
       </c>
       <c r="E21" t="s">
         <v>27</v>
@@ -1086,7 +1086,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>2201</v>
+        <v>20201</v>
       </c>
       <c r="E22" t="s">
         <v>28</v>
@@ -1109,7 +1109,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>2203</v>
+        <v>20203</v>
       </c>
       <c r="E23" t="s">
         <v>29</v>
@@ -1132,7 +1132,7 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>2205</v>
+        <v>20205</v>
       </c>
       <c r="E24" t="s">
         <v>30</v>
@@ -1155,7 +1155,7 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>2207</v>
+        <v>20207</v>
       </c>
       <c r="E25" t="s">
         <v>31</v>
@@ -1178,7 +1178,7 @@
         <v>7</v>
       </c>
       <c r="D26">
-        <v>2210</v>
+        <v>20210</v>
       </c>
       <c r="E26" t="s">
         <v>32</v>
@@ -1201,7 +1201,7 @@
         <v>7</v>
       </c>
       <c r="D27">
-        <v>2211</v>
+        <v>20211</v>
       </c>
       <c r="E27" t="s">
         <v>33</v>
@@ -1224,7 +1224,7 @@
         <v>7</v>
       </c>
       <c r="D28">
-        <v>2215</v>
+        <v>20215</v>
       </c>
       <c r="E28" t="s">
         <v>34</v>
@@ -1247,7 +1247,7 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>2216</v>
+        <v>20216</v>
       </c>
       <c r="E29" t="s">
         <v>35</v>
@@ -1270,7 +1270,7 @@
         <v>7</v>
       </c>
       <c r="D30">
-        <v>2218</v>
+        <v>20218</v>
       </c>
       <c r="E30" t="s">
         <v>36</v>
@@ -1400,5 +1400,6 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/db.xlsx
+++ b/db.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeacherCHO\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\OneDrive - 영산고등학교\학교업무\생활기록부\2026. 생기부\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -139,9 +139,6 @@
     <t>자동차 정비소의 리프트 추락을 소재로 정비사 관점에서 리프트의 안전성을 물리적으로 검증하는 PBL 시나리오를 창작함. 차량이 내려앉을 때 발생하는 위치에너지를 위치에너지 공식으로 구하고, 이를 스프링이 흡수한다고 볼 때 최대 압축 거리로부터 스프링이 견뎌야 할 힘을 일-에너지 관계로 역산하는 흐름을 세움. 위치에너지와 일, 충격량을 하나의 안전 검증 목표 아래 연결하려 시도하고, 충돌 시간을 늘려 충격력을 낮추는 방향에서 스프링 보강과 이중 잠금장치라는 개선안을 제안함. 실제 정비 현장의 위험을 물리량으로 번역해 안전 기준을 따지는 접근에서 개념의 실용적 적용력을 보임. 심화 활동에서는 운동량과 충격량의 관계를 낙하 물체의 충격 흡수 원리로 확장하여, 착지 순간 관절을 굽혀 충돌 시간을 늘리면 평균 충격력이 감소함을 설명하고 낙하 단계별 위치에너지와 운동에너지의 전환 과정을 정리함. 이를 자동차 서스펜션이나 기계 장비의 방진 설계가 외부 충격을 분산시키는 원리와 연결지어, 기계공학 진로와 이어 충격 흡수와 구조적 안정성의 관계를 탐구하려는 자기주도적 학습 태도가 돋보임.</t>
   </si>
   <si>
-    <t>비 오는 날 경사로에서 전동킥보드가 자전거와 충돌한 사고를 소재로 학교 안전 검토위원 역할을 맡아 안전장치의 실효성을 분석하는 PBL 시나리오를 창작함. 역학적 에너지 보존으로 충돌 직전 속력을, 운동량 보존으로 충돌 후 공동 속력을, 다시 충격량과 충돌 시간으로 탑승자가 받는 평균 충격력을 구하는 세 단계를 매끄럽게 이어감. 산출한 값을 안전 기준과 견주어 현재 장치가 기준을 충족함을 논리적으로 판정하고, 충돌 시간을 더 늘리는 흡수 구조로 충격력을 한층 낮추는 개선 방향까지 제시함. 여러 보존 법칙을 정해진 순서대로 적용해 하나의 결론에 도달하는 구성이 매우 체계적이며, 개념 사이의 연결을 놓치지 않는 탐구 역량과 문제 해결력을 꾸준히 발휘하는 모습이 관찰됨.</t>
-  </si>
-  <si>
     <t>초고층 건설 현장의 타워크레인 전복 위험을 소재로 안전진단 전문가 역할을 맡아 돌림힘 평형으로 평형추를 설계하는 PBL 시나리오를 창작함. 자재와 평형추가 만드는 돌림힘을 회전축 기준으로 각각 계산하고, 자재를 든 상황과 내려놓은 상황을 나누어 모멘트를 비교하는 이원적 분석이 돋보임. 자재를 내려놓는 순간 평형추만 남아 반대편으로 전복될 수 있음을 포착하고, 두 상황의 안전 조건을 모두 만족하는 평형추의 질량 범위 3000~4000kg을 부등식으로 도출함. 정적 평형을 작업 국면의 변화로 나누어 다루는 접근에서 돌림힘 개념에 대한 깊은 이해와 구조적 사고력을 보임. 심화 활동에서는 패러데이 전자기 유도 법칙을 심화하여 무선 충전 기술의 작동 원리를 탐구함. 코일에 흐르는 교류 전류가 시간에 따라 변화하는 자기장을 형성하고, 이 자기장이 수신 코일을 통과하며 유도 기전력이 발생하는 과정을 수식으로 분석함. 결합 계수와 거리에 따라 전력 전송 효율이 달라지는 한계를 조사하고 보완 방식까지 탐구함. 관련 독서활동으로 패러데이의 실험적 접근 과정을 다룬 책을 읽고, 전기전자공학 진로와 연계하여 이론적 개념을 실제 소자의 전력 전송 문제와 연결짓는 탐구 역량을 보임.</t>
   </si>
   <si>
@@ -181,9 +178,6 @@
     <t>우주 탐사선을 소행성에 충돌시켜 궤도를 바꾸는 실험과 공룡 멸종 시기 지층에서의 이리듐 발견을 엮어 소행성 궤도 변경을 다루는 독창적인 PBL 시나리오를 창작함. 경계층 이리듐의 총량에서 소행성 지름을, 충돌 규모에서 운동에너지와 질량을 역산하는 과정을 통해 과학사적 발견을 물리량으로 재구성하는 넓은 시야를 보임. 인공위성과 소행성의 충돌에 운동량 보존을 적용하고, 작용과 반작용으로 파편이 튀는 현상까지 궤도 변화의 요인으로 고려해 충격량으로 속도 변화를 추정하는 야심찬 구성을 시도함. 천체 규모의 현상을 학교에서 배운 보존 법칙으로 다루려는 도전적인 접근에서 물리에 대한 폭넓은 관심과 지적 호기심이 두드러짐. 심화 활동에서는 특수 상대성 이론을 심화하여 블랙홀 주변에서 나타나는 시간 팽창 현상을 탐구함. 빛의 속력이 모든 관성계에서 동일하다는 원리를 바탕으로, 강한 중력장에 접근하는 관측자와 멀리 있는 관측자 사이에 시간이 다르게 측정되는 사고 실험을 구성하여 설명함. 관련 독서활동으로 물리 교양서를 읽고 상대성 이론의 기본 개념을 이해하고, 천문학 진로와 연계하여 특수 상대성 이론을 천체물리학적 현상과 연결지어 이해하려는 자기주도적 탐구 태도를 보임.</t>
   </si>
   <si>
-    <t>급커브 구간의 차량 충돌 사고를 소재로 교통안전 공학자 역할에서 충격 흡수형 방호벽을 설계하는 PBL 시나리오를 창작함. 단단한 콘크리트 벽 대신 충돌 시간을 늘리는 구조가 왜 탑승자를 보호하는지를 충격량과 운동량의 관계로 설명하고, 질량과 충돌 직전 속도가 같으면 충격량은 일정하되 시간을 늘리면 평균 힘이 줄어든다는 핵심을 명확히 짚음. 충돌 시간을 열 배 늘리면 평균 힘이 10분의 1로 줄어듦을 계산으로 보이고, 내부를 비운 드럼통이나 벌집 구조 완충재라는 구체적인 재질과 구조를 함께 제안함. 물리 원리에서 재료 설계까지 일관되게 이어가는 과정에서 개념의 실용적 적용력과 성실한 탐구 태도를 뚜렷하게 보임.</t>
-  </si>
-  <si>
     <t>고속도로 추돌 사고에서 에어백 설계가 국제 안전 기준을 충족하는지를 판별하는 사고 조사 물리학자 역할의 PBL 시나리오를 창작함. 질량이 다른 두 차량이 충돌 후 하나로 붙어 움직이는 완전 비탄성 충돌 상황을 설정하고, 운동량 보존으로 공동 속력을 구한 뒤 탑승자의 운동량 변화와 충돌 시간으로 평균 충격력을 산출해 국제 안전 기준과 비교하는 흐름을 세움. 에어백이 충돌 시간을 늘리면 충격력이 더 낮아짐을 계산해 추가적인 안전 향상 방안의 근거로 삼음. 완전 비탄성 충돌의 운동량 보존과 충격량을 결합해 안전 기준 판정에 이르는 구성이 논리적이며, 개념을 실제 사고 분석에 적용하는 역량과 차분한 탐구 자세가 관찰됨. 심화 활동에서는 등가속도 운동의 기본 식을 심화하여 자동차의 제동 거리를 계산하는 활동을 수행함. 속도와 가속도, 이동 거리의 관계식을 이용해 제동 시간과 제동 거리를 구하고, 속도가 두 배가 되면 제동 거리가 네 배로 증가함을 확인함. 수학교육 진로와 연계하여 물리 현상을 수학적 함수로 표현하고 이를 실생활 사례로 설명하는 방법을 탐구하려는 모습을 보임.</t>
   </si>
   <si>
@@ -218,13 +212,19 @@
   </si>
   <si>
     <t>체육대회 줄다리기의 패인을 마찰력과 뉴턴 운동 법칙으로 규명하는 승리 전략 분석 PBL 시나리오를 창작함. 힘의 세기가 아니라 운동화와 바닥 사이의 마찰, 무게중심, 자세가 결과를 가른다는 관찰을 영상 분석에서 스스로 이끌어냄. 최대 정지 마찰력이 수직항력과 마찰계수의 곱으로 정해짐을 이해하고, 체중으로부터 수직항력을 구한 뒤 버틸 수 있는 최대 힘을 산출함. 경기를 마찰력이라는 지표로 환원해 팀 배치와 신발 선택의 근거를 마련하며 물리 개념을 실제 전략으로 연결하는 사고를 보임. 심화 활동에서는 열의 전달과 물의 상태 변화 원리를 친환경 건축의 열환경 개선 기술로 확장하여 탐구함. 여름철 건물의 온도 상승이 태양 복사에너지 흡수에서 시작해 전도와 대류로 실내에 퍼지는 세 전달 방식의 결과임을 정리함. 물이 증발할 때 주변 열을 흡수해 표면 온도를 낮추는 증발냉각 원리를 상태 변화와 에너지 출입 관점에서 설명하고, 습도가 높은 우리나라 여름에는 증발 속도가 느려 냉각 효과가 줄 수 있어 단열이나 자연환기와 병행해야 효과적이라는 결론을 도출함.</t>
+  </si>
+  <si>
+    <t>비 오는 날 경사로에서 전동킥보드와 자전거가 충돌한 사고로 안전장치의 실효성을 분석하는 PBL 시나리오를 창작함. 역학적 에너지 보존으로 충돌 직전 속력을, 운동량 보존으로 충돌 후 공동 속력을, 충격량과 충돌 시간으로 평균 충격력을 구하는 세 단계를 매끄럽게 이어감. 산출한 값을 안전 기준과 견주어 장치의 충족 여부를 판정하고, 충돌 시간을 늘리는 흡수 구조로 충격력을 낮추는 개선 방향을 제시함. 여러 보존 법칙을 순서대로 적용하는 체계적 구성과 개념 연결 역량을 보임. 심화 활동에서는 무선전력전송 기술의 원리와 발전 방향을 다양하게 분석함. 송신 코일의 교류 자기장으로 수신 코일에 유도 전류가 생기는 자기유도 방식과, 공진 주파수가 일치할 때 에너지가 전달되는 자기공진 방식을 전송 거리와 효율로 비교함. 결합계수와 공진 조건, 코일의 품질계수가 효율을 좌우하므로 코일 결합과 함께 저항 손실 감소도 고려해야 함을 이해함. 이를 통해 코일 수 증가가 곧 효율 향상은 아니며 시스템 최적화가 관건임을 파악하고, 효율 향상과 국제 표준화를 핵심 과제로 정리함. 전자기 유도와 공진 개념이 첨단 기술의 기반 원리임을 탐구하려는 태도가 돋보임.</t>
+  </si>
+  <si>
+    <t>급커브 구간의 차량 충돌 사고를 소재로 충격 흡수형 방호벽을 설계하는 PBL 시나리오를 창작함. 단단한 벽 대신 충돌 시간을 늘리는 구조가 탑승자를 보호하는 이유를 충격량과 운동량의 관계로 설명하고, 충격량이 같아도 시간을 늘리면 평균 힘이 줄어든다는 핵심을 명확히 짚음. 충돌 시간을 열 배 늘리면 평균 힘이 10분의 1로 줄어듦을 보이고, 내부를 비운 드럼통이나 벌집 구조 완충재를 제안함. 물리 원리에서 재료 설계까지 이어가는 과정에서 개념의 실용적 적용력을 보임. 심화 활동에서는 전기와 자기 단원의 개념으로 자기공명영상 장치의 작동 원리를 설명함. 저항이 없는 초전도 코일에 전류를 흘려 강하고 균일한 자기장을 만드는 과정을 전류에 의한 자기장 원리로 설명하고, 인체 속 수소 원자핵이 강한 외부 자기장에서 일정하게 정렬되는 현상을 물질의 자성 개념과 연결함. 고주파를 차단하면 원자핵이 되돌아가며 자기장이 변하고, 자속 변화가 수신 코일에 패러데이 전자기 유도로 유도 전류를 일으켜 조직별 신호 차이가 명암 영상으로 나타남을 정리함. 생명공학 연구원을 희망하는 진로와 연계하여 생명 현상도 물리 법칙으로 설명된다는 관점에서 교과 개념을 의료 진단 기술과 연결짓는 태도가 돋보임.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,6 +245,13 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -279,8 +286,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -288,8 +296,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="표준 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -678,7 +687,7 @@
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>6969</v>
@@ -701,7 +710,7 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G5">
         <v>4463</v>
@@ -724,7 +733,7 @@
         <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G6">
         <v>6522</v>
@@ -747,7 +756,7 @@
         <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G7">
         <v>9757</v>
@@ -770,7 +779,7 @@
         <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8">
         <v>6607</v>
@@ -793,7 +802,7 @@
         <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G9">
         <v>6991</v>
@@ -816,7 +825,7 @@
         <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G10">
         <v>2045</v>
@@ -839,7 +848,7 @@
         <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G11">
         <v>4843</v>
@@ -862,7 +871,7 @@
         <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G12">
         <v>8111</v>
@@ -885,7 +894,7 @@
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G13">
         <v>6085</v>
@@ -908,7 +917,7 @@
         <v>20</v>
       </c>
       <c r="F14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G14">
         <v>2669</v>
@@ -931,7 +940,7 @@
         <v>21</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G15">
         <v>7115</v>
@@ -954,7 +963,7 @@
         <v>22</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G16">
         <v>8478</v>
@@ -977,7 +986,7 @@
         <v>23</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G17">
         <v>6678</v>
@@ -1000,7 +1009,7 @@
         <v>24</v>
       </c>
       <c r="F18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G18">
         <v>7675</v>
@@ -1023,7 +1032,7 @@
         <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G19">
         <v>8517</v>
@@ -1046,7 +1055,7 @@
         <v>26</v>
       </c>
       <c r="F20" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="G20">
         <v>7491</v>
@@ -1069,7 +1078,7 @@
         <v>27</v>
       </c>
       <c r="F21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G21">
         <v>5132</v>
@@ -1092,7 +1101,7 @@
         <v>28</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G22">
         <v>9489</v>
@@ -1115,7 +1124,7 @@
         <v>29</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G23">
         <v>8555</v>
@@ -1138,7 +1147,7 @@
         <v>30</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G24">
         <v>7394</v>
@@ -1161,7 +1170,7 @@
         <v>31</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G25">
         <v>7637</v>
@@ -1184,7 +1193,7 @@
         <v>32</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G26">
         <v>5335</v>
@@ -1207,7 +1216,7 @@
         <v>33</v>
       </c>
       <c r="F27" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G27">
         <v>9654</v>
@@ -1230,7 +1239,7 @@
         <v>34</v>
       </c>
       <c r="F28" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G28">
         <v>4420</v>
@@ -1253,7 +1262,7 @@
         <v>35</v>
       </c>
       <c r="F29" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G29">
         <v>2298</v>
@@ -1276,7 +1285,7 @@
         <v>36</v>
       </c>
       <c r="F30" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G30">
         <v>5131</v>
